--- a/astro-site/public/dl/kit-tareas-bar/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-bar/03-tareas-manager.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Diario Manager" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Semanal Manager" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diario Manager" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanal Manager" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Diario Manager'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal Manager'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual Manager'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -119,7 +123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -141,49 +145,108 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -543,15 +606,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -559,6 +623,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -587,8 +652,33 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -597,18 +687,18 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -625,10 +715,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -653,7 +744,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -668,18 +759,16 @@
           <t xml:space="preserve">  Antes de Abrir</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -705,10 +794,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -734,10 +821,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -763,10 +848,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -792,10 +875,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -820,24 +901,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Durante el Servicio</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -863,10 +943,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -892,10 +970,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -921,10 +997,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -950,10 +1024,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -978,24 +1050,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cierre de Día</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="20" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1021,10 +1092,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1050,10 +1119,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="21" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1079,10 +1146,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1108,10 +1173,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="21" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1136,6 +1199,8 @@
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="15" t="n"/>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
@@ -1144,17 +1209,19 @@
       </c>
       <c r="D27" s="16">
         <f>COUNTIF(F5:F25,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F27" s="16" t="n">
-        <v>15</v>
-      </c>
-    </row>
+      <c r="F27" s="16">
+        <f>COUNTIF(B5:B25,"?*")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
@@ -1162,13 +1229,17 @@
         </is>
       </c>
       <c r="B29" s="15" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="20" t="n"/>
       <c r="E29" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
-    </row>
+      <c r="G29" s="20" t="n"/>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
@@ -1187,12 +1258,26 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G25">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1201,18 +1286,18 @@
   <sheetPr>
     <tabColor rgb="00FF8C00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1229,10 +1314,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1257,7 +1343,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1272,18 +1358,16 @@
           <t xml:space="preserve">  Lunes — Inventario</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1309,10 +1393,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1338,10 +1420,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1367,10 +1447,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1396,10 +1474,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1424,24 +1500,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martes — Equipo</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1467,10 +1542,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1496,10 +1569,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1524,24 +1595,23 @@
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="15" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Miércoles — Calidad</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="20" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1567,10 +1637,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1596,10 +1664,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1625,10 +1691,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1653,24 +1717,23 @@
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="15" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Jueves — Carta y Creatividad</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="20" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="21" t="n">
+        <v>13</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1696,10 +1759,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1725,10 +1786,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="21" t="n">
+        <v>15</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -1754,10 +1813,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="21" t="n">
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -1782,24 +1839,23 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Viernes — Pre Fin de Semana</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="20" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="21" t="n">
+        <v>17</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -1825,10 +1881,8 @@
       <c r="G30" s="15" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A31" s="21" t="n">
+        <v>18</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -1854,10 +1908,8 @@
       <c r="G31" s="15" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A32" s="21" t="n">
+        <v>19</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
@@ -1883,10 +1935,8 @@
       <c r="G32" s="15" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A33" s="21" t="n">
+        <v>20</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -1911,6 +1961,8 @@
       <c r="F33" s="14" t="n"/>
       <c r="G33" s="15" t="n"/>
     </row>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
@@ -1919,17 +1971,19 @@
       </c>
       <c r="D36" s="16">
         <f>COUNTIF(F5:F34,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F36" s="16" t="n">
-        <v>20</v>
-      </c>
-    </row>
+      <c r="F36" s="16">
+        <f>COUNTIF(B5:B34,"?*")</f>
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
@@ -1937,13 +1991,17 @@
         </is>
       </c>
       <c r="B38" s="15" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="20" t="n"/>
       <c r="E38" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F38" s="15" t="n"/>
-    </row>
+      <c r="G38" s="20" t="n"/>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
@@ -1964,12 +2022,26 @@
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="F38:G38"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G34">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27 F30 F31 F32 F33" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1978,18 +2050,18 @@
   <sheetPr>
     <tabColor rgb="008B4513"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2006,10 +2078,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2034,7 +2107,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2049,18 +2122,16 @@
           <t xml:space="preserve">  Financiero</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -2086,10 +2157,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2115,10 +2184,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2144,10 +2211,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2172,24 +2237,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="15" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Mantenimiento</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="20" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -2215,10 +2279,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -2244,10 +2306,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2273,10 +2333,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2302,10 +2360,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2330,24 +2386,23 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Evaluación</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="20" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -2373,10 +2428,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -2402,10 +2455,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -2431,10 +2482,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="21" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -2459,6 +2508,8 @@
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="15" t="n"/>
     </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
@@ -2467,17 +2518,19 @@
       </c>
       <c r="D25" s="16">
         <f>COUNTIF(F5:F23,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F25" s="16" t="n">
-        <v>13</v>
-      </c>
-    </row>
+      <c r="F25" s="16">
+        <f>COUNTIF(B5:B23,"?*")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
@@ -2485,13 +2538,17 @@
         </is>
       </c>
       <c r="B27" s="15" t="n"/>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="20" t="n"/>
       <c r="E27" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F27" s="15" t="n"/>
-    </row>
+      <c r="G27" s="20" t="n"/>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
@@ -2510,11 +2567,25 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F19 F20 F21 F22" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-bar/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-bar/03-tareas-manager.xlsx
@@ -13,9 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$44</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Diario Manager'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal Manager'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$44</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual Manager'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,8 +100,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -120,6 +138,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -193,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -231,6 +254,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -608,63 +686,218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>03 — Tareas del Manager · Bar / Cocktails</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Checklists para el/la responsable del bar.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>▸ Diario: lo que hay que revisar cada día</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>▸ Semanal: tareas organizadas por día</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>▸ Mensual: revisiones periódicas</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="B9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>El registro de jornada es obligatorio</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>▸ Desde 2019 hay que registrar cada día la entrada, la salida y las pausas de todo el equipo, y conservar esos registros cuatro años. En un bar con cierres a las 02:30 es también la única prueba de las horas que se han hecho de más.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>▸ La tarea diaria está en «Diario Manager» (cerrar y validar el registro del día) y la mensual en «Mensual Manager» (archivar el mes). El kit no sustituye a tu sistema de fichaje: te recuerda cerrarlo y guardarlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>▸ Estás en 03-tareas-manager.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="35" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -689,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -739,7 +972,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -754,517 +987,605 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Antes de Abrir</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="20" t="n"/>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="n">
+      <c r="A6" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Revisar reservas del día (grupos, eventos privados, VIPs)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="33" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Verificar asistencia del equipo y cubrir bajas</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="33" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n">
+      <c r="A8" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Revisar stock crítico (spirits, cerveza, hielo, cítricos)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="33" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Confirmar entregas de proveedores del día</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="33" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>Briefing con equipo: cóctel del día, eventos, notas</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="33" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Durante el Servicio</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="20" t="n"/>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Supervisar calidad de servicio y cócteles</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="33" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Control de ambiente: música, iluminación, temperatura</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="33" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Gestionar quejas o incidencias con clientes</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="33" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="n">
+      <c r="A16" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>Supervisar cumplimiento de normativa (no servir a menores, aforo)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="33" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>Evaluar tiempos de servicio (objetivo: &lt;3 min cóctel, &lt;1 min cerveza)</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="33" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="34" t="n"/>
+      <c r="G18" s="34" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cierre de Día</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="19" t="n"/>
-      <c r="G19" s="20" t="n"/>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
+      <c r="G19" s="27" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="28" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Revisar caja y cuadrar con TPV</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>Revisar el DESCUADRE que ha quedado en «Cierre de Caja» del fichero 09-apertura-cierre-caja.xlsx y firmarlo: el manager valida el arqueo, no lo vuelve a contar</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="33" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Revisar inventario rápido de botellas abiertas</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="33" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="n">
+      <c r="A22" s="28" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Anotar mermas (rotura cristalería, derrames, producto caducado)</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Revisar las mermas que ha anotado la barra al cierre (cristalería rota, derrames, cócteles devueltos y producto caducado) y trasladarlas al control del pour cost</t>
+        </is>
+      </c>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="F22" s="32" t="n"/>
+      <c r="G22" s="33" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>Planificar necesidades del día siguiente</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="33" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="n">
+      <c r="A24" s="28" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>Cerrar y validar el registro diario de jornada del equipo (entradas, salidas y pausas), incluidas las horas de cierre pasadas las 00:00</t>
+        </is>
+      </c>
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="33" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>Verificar cierre correcto del local</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="33" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n"/>
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="33" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="35" t="n"/>
+      <c r="B27" s="36" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="33" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n"/>
+      <c r="B28" s="36" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="33" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="n"/>
+      <c r="B29" s="36" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="32" t="n"/>
+      <c r="G29" s="33" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="n"/>
+      <c r="B30" s="36" t="n"/>
+      <c r="C30" s="30" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="33" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D27" s="16">
-        <f>COUNTIF(F5:F25,"✓")</f>
+      <c r="D32" s="16">
+        <f>COUNTIFS(B5:B30,"?*",F5:F30,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F27" s="16">
-        <f>COUNTIF(B5:B25,"?*")</f>
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="F32" s="16">
+        <f>COUNTIF(B5:B30,"?*")-COUNTIF(F5:F30,"N/A")</f>
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="B34" s="37" t="n"/>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="20" t="n"/>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="F34" s="37" t="n"/>
+      <c r="G34" s="20" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
-    <mergeCell ref="F29:G29"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="F34:G34"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G25">
+  <conditionalFormatting sqref="A5:G30">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1288,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1353,682 +1674,759 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Lunes — Inventario</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="20" t="n"/>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="n">
+      <c r="A6" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Inventario completo de spirits (botellas llenas + nivel de abiertas)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="33" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Inventario de cerveza (barriles + botellas + latas)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="33" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n">
+      <c r="A8" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Inventario de vinos (bodega + cámara)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="33" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Inventario de refrescos, zumos, jarabes y mixers</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="33" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>Hacer pedidos semanales a distribuidores</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="33" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martes — Equipo</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="20" t="n"/>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Revisar cuadrante de turnos de la semana</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="33" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Reunión con equipo (feedback, formación, objetivos)</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="33" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Revisar formación de personal nuevo (mentoring)</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="33" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="34" t="n"/>
+      <c r="G16" s="34" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Miércoles — Calidad</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n"/>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="19" t="n"/>
-      <c r="F17" s="19" t="n"/>
-      <c r="G17" s="20" t="n"/>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="26" t="n"/>
+      <c r="G17" s="27" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="n">
+      <c r="A18" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Auditar 3 cócteles al azar (receta, presentación, tiempo)</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="33" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Revisar registros de temperatura de cámaras</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>Revisar registros de temperatura de cámaras (refrigeración 0-4 °C) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="33" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="28" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>Comprobar FIFO en cámaras y bodega</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="33" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Verificar limpieza profunda de barra (detrás, debajo)</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="33" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="34" t="n"/>
+      <c r="D22" s="34" t="n"/>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="34" t="n"/>
+    </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Jueves — Carta y Creatividad</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="20" t="n"/>
+      <c r="B23" s="26" t="n"/>
+      <c r="C23" s="26" t="n"/>
+      <c r="D23" s="26" t="n"/>
+      <c r="E23" s="26" t="n"/>
+      <c r="F23" s="26" t="n"/>
+      <c r="G23" s="27" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="n">
+      <c r="A24" s="28" t="n">
         <v>13</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>Revisar ventas por cóctel (top 5 y bottom 5)</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="33" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="n">
+      <c r="A25" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>Desarrollar o rotar cóctel de la semana</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="33" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="n">
+      <c r="A26" s="28" t="n">
         <v>15</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>Actualizar carta si hay cambios</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="33" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="n">
+      <c r="A27" s="28" t="n">
         <v>16</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>Preparar contenido RRSS (foto de cóctel estrella)</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15" t="n"/>
-    </row>
-    <row r="28"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="33" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="34" t="n"/>
+      <c r="D28" s="34" t="n"/>
+      <c r="E28" s="34" t="n"/>
+      <c r="F28" s="34" t="n"/>
+      <c r="G28" s="34" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Viernes — Pre Fin de Semana</t>
         </is>
       </c>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="20" t="n"/>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+      <c r="E29" s="26" t="n"/>
+      <c r="F29" s="26" t="n"/>
+      <c r="G29" s="27" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="n">
+      <c r="A30" s="28" t="n">
         <v>17</v>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>Verificar stock para fin de semana (30-50% más que entre semana)</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="33" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="n">
+      <c r="A31" s="28" t="n">
         <v>18</v>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>Confirmar turnos reforzados de fin de semana</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="F31" s="32" t="n"/>
+      <c r="G31" s="33" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="n">
+      <c r="A32" s="28" t="n">
         <v>19</v>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>Verificar stock de hielo extra</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="F32" s="32" t="n"/>
+      <c r="G32" s="33" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="n">
+      <c r="A33" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>Preparar batches de cócteles de alta rotación</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="15" t="n"/>
-    </row>
-    <row r="34"/>
-    <row r="35"/>
+      <c r="F33" s="32" t="n"/>
+      <c r="G33" s="33" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="n"/>
+      <c r="B34" s="36" t="n"/>
+      <c r="C34" s="30" t="n"/>
+      <c r="D34" s="31" t="n"/>
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="32" t="n"/>
+      <c r="G34" s="33" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="n"/>
+      <c r="B35" s="36" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="31" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="33" t="n"/>
+    </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D36" s="16">
-        <f>COUNTIF(F5:F34,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F36" s="16">
-        <f>COUNTIF(B5:B34,"?*")</f>
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="37"/>
+      <c r="A36" s="35" t="n"/>
+      <c r="B36" s="36" t="n"/>
+      <c r="C36" s="30" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="32" t="n"/>
+      <c r="G36" s="33" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="n"/>
+      <c r="B37" s="36" t="n"/>
+      <c r="C37" s="30" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="32" t="n"/>
+      <c r="G37" s="33" t="n"/>
+    </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="20" t="n"/>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="20" t="n"/>
+      <c r="A38" s="35" t="n"/>
+      <c r="B38" s="36" t="n"/>
+      <c r="C38" s="30" t="n"/>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="31" t="n"/>
+      <c r="F38" s="32" t="n"/>
+      <c r="G38" s="33" t="n"/>
     </row>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D40" s="16">
+        <f>COUNTIFS(B5:B38,"?*",F5:F38,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F40" s="16">
+        <f>COUNTIF(B5:B38,"?*")-COUNTIF(F5:F38,"N/A")</f>
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B42" s="37" t="n"/>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F42" s="37" t="n"/>
+      <c r="G42" s="20" t="n"/>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="10">
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F42:G42"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G34">
+  <conditionalFormatting sqref="A5:G38">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27 F30 F31 F32 F33 F34 F35 F36 F37 F38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2052,7 +2450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2102,7 +2500,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2117,463 +2515,551 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Financiero</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="20" t="n"/>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="n">
+      <c r="A6" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Revisar pour cost (objetivo: 18-22% spirits, 25-30% cerveza)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>1ª semana</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="33" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Analizar mermas del mes (objetivo: &lt;3%)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>1ª semana</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="33" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n">
+      <c r="A8" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Comparar ventas mes actual vs. anterior y mismo mes año anterior</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t>1ª semana</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="33" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Revisar rentabilidad por categoría (cócteles, cerveza, vino, café)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>1ª semana</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
-    </row>
-    <row r="10"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="33" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>Archivar los registros de jornada del mes (hay que conservarlos 4 años a disposición de la Inspección de Trabajo)</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>1ª semana</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="33" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="34" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Mantenimiento</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n"/>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="20" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="27" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Limpieza profunda de líneas de grifo (con producto específico)</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>2ª semana</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="33" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Mantenimiento de máquina de espresso (descalcificar, cambiar juntas)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E14" s="31" t="inlineStr">
         <is>
           <t>2ª semana</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Revisar estado de cámaras frigoríficas (limpieza, temperatura)</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="33" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Revisar el estado de las cámaras frigoríficas: limpieza, cierre de puertas y temperatura (refrigeración 0-4 °C) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>2ª semana</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="33" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>Verificar estado de cristalería (reponer piezas rotas/rayadas)</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="inlineStr">
         <is>
           <t>2ª semana</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="33" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>Calibrar termómetros y sondas</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>2ª semana</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="33" t="n"/>
+    </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="34" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="34" t="n"/>
+      <c r="G18" s="34" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Evaluación</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="19" t="n"/>
-      <c r="F18" s="19" t="n"/>
-      <c r="G18" s="20" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
+      <c r="G19" s="27" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>Evaluación informal del equipo (skills, actitud, puntualidad)</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>3ª semana</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="33" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Visitar 2-3 bares de la competencia (tendencias, precios, servicio)</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>3ª semana</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="33" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>Proponer nuevos cócteles para la carta</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>3ª semana</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="F22" s="32" t="n"/>
+      <c r="G22" s="33" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>Revisar reviews online (Google, TripAdvisor, redes)</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>4ª semana</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
-    </row>
-    <row r="23"/>
-    <row r="24"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="33" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="n"/>
+      <c r="B24" s="36" t="n"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="31" t="n"/>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="33" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="35" t="n"/>
+      <c r="B25" s="36" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="33" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n"/>
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="33" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="n"/>
+      <c r="B27" s="36" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="33" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n"/>
+      <c r="B28" s="36" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="33" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D25" s="16">
-        <f>COUNTIF(F5:F23,"✓")</f>
+      <c r="D30" s="16">
+        <f>COUNTIFS(B5:B28,"?*",F5:F28,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F25" s="16">
-        <f>COUNTIF(B5:B23,"?*")</f>
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="F30" s="16">
+        <f>COUNTIF(B5:B28,"?*")-COUNTIF(F5:F28,"N/A")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="B32" s="37" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="20" t="n"/>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="F32" s="37" t="n"/>
+      <c r="G32" s="20" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="F32:G32"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G23">
+  <conditionalFormatting sqref="A5:G28">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
